--- a/Documentation/Memory Map.xlsx
+++ b/Documentation/Memory Map.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t xml:space="preserve">JakelynnOS Memory Map</t>
   </si>
@@ -37,22 +37,46 @@
     <t xml:space="preserve">End</t>
   </si>
   <si>
+    <t xml:space="preserve">Use (phys range)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0x00000000</t>
   </si>
   <si>
     <t xml:space="preserve">0x00010000</t>
   </si>
   <si>
+    <t xml:space="preserve">SEPT (0x0-0x10000)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Identity Map</t>
   </si>
   <si>
+    <t xml:space="preserve">0x000100000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0xBFFFFFFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User Area</t>
+  </si>
+  <si>
     <t xml:space="preserve">0x00001000</t>
   </si>
   <si>
     <t xml:space="preserve">SEPT (System Entry Point  Table)</t>
   </si>
   <si>
-    <t xml:space="preserve">0x000A8000</t>
+    <t xml:space="preserve">0xC0000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0xFFFFFFFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kernel Area (0x00100000-0x0010FFFF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x000A0000</t>
   </si>
   <si>
     <t xml:space="preserve">0x000BFFFF</t>
@@ -61,49 +85,55 @@
     <t xml:space="preserve">Video Area (we use 0xB80000-0xBFFFF)</t>
   </si>
   <si>
-    <t xml:space="preserve">0x00FFFFFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0x000C0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0X00FFFFFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMA Memory</t>
+    <t xml:space="preserve">0xFF7E8000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0xFF7FFFFFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video Memory (0xA8000-0xBFFFF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x000C00000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x004BFFFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page Table Entries (1024 of them) (done)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0xFF800000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page Table Entries (0x00400000-0x007FFFFF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0x004C0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User Memory Area</t>
   </si>
   <si>
     <t xml:space="preserve">0x00100000</t>
   </si>
   <si>
-    <t xml:space="preserve">0x0104FFFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0x0103FFFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Page Table Entries (1024 of them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0x01040000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0xBFFFFFFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0xFFFFFFFF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User Memory Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0xC0000000</t>
-  </si>
-  <si>
     <t xml:space="preserve">0x0010FFFF</t>
   </si>
   <si>
     <t xml:space="preserve">Kernel Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video and page tables are non-swapable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPT is non-swapable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final PTE Range will be done after MULTIBOOT is saved</t>
   </si>
 </sst>
 </file>
@@ -113,11 +143,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -139,17 +170,26 @@
       <sz val="20"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Ariel"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -194,24 +234,40 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,160 +394,177 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="43.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="43.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>9</v>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>12</v>
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="A8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>20</v>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>24</v>
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+      <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>27</v>
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
